--- a/tests/acceptance/atp1/labels/complementary.xlsx
+++ b/tests/acceptance/atp1/labels/complementary.xlsx
@@ -1,17 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet name="Labels" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,15 +45,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -294,7 +300,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -303,13 +309,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -343,17 +349,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -408,8 +403,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -492,925 +485,1845 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="39.59999847412109" customHeight="1">
+      <c r="A2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>AGE1002S</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Science, 2026</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="26.39999961853027" customHeight="1">
+      <c r="A3" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>BIO1000F</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>4 of 6</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>practical</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Science, 2026</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Fourth of six rows is the Tuesday alternative, after the lecture, tutorial and Monday practical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26.39999961853027" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>BIO1004S</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>2 of 6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Science, 2026</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>One tutorial per week, by arrangement. No day or time is printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26.39999961853027" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>BUS2024S</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52.79999923706055" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>ECO1010F</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>4 of 5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>The handbook lists four slots without explicitly saying "or". Follow the source workbook's documented alternative-group reading and label this row's slot. Fourth lecture slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.79999923706055" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>ECO1011S</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>1 of 5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>The handbook lists four slots without explicitly saying "or". Follow the source workbook's documented alternative-group reading and label this row's slot. First lecture slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.79999923706055" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>ECO1011S</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>2 of 5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>The handbook lists four slots without explicitly saying "or". Follow the source workbook's documented alternative-group reading and label this row's slot. Second lecture slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>ECO1008S</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>3 of 4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Engineering &amp; the Built Environment (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>The handbook lists four slots without explicitly saying "or". Follow the source workbook's documented alternative-group reading and label this row's slot. Third lecture slot. The printed "Wedesday" is labelled Wednesday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.79999923706055" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>ECO2007S</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>The handbook joins the two slots with "and". Follow the source workbook's documented alternative-group reading; the printed wording does not itself settle attendance. First slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.79999923706055" customHeight="1">
+      <c r="A11" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>ECO2007S</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>2 of 2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Commerce (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>The handbook joins the two slots with "and". Follow the source workbook's documented alternative-group reading; the printed wording does not itself settle attendance. Second slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.39999961853027" customHeight="1">
+      <c r="A12" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>ELL1013F</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="26.39999961853027" customHeight="1">
+      <c r="A13" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>FAM1000S</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="26.39999961853027" customHeight="1">
+      <c r="A14" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>FAM2004S</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>GEO1009F</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>2 of 5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>practical</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Science, 2026</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>The course entry on p. 153 states the lectures only. The Practical/Tutorial column on p. 247 supplies this afternoon slot. Follow the documented combined-kind convention: practical. Second of five rows is the Monday alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.39999961853027" customHeight="1">
+      <c r="A16" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>HST1013F</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="26.39999961853027" customHeight="1">
+      <c r="A17" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>PHI1010S</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="26.39999961853027" customHeight="1">
+      <c r="A18" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>PHI1025F</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="39.59999847412109" customHeight="1">
+      <c r="A19" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>PHI2043F</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>367</v>
+      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>First alternative is the 3rd period. The heading is printed PHI2043FS on p. 367; its times continue on p. 368.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26.39999961853027" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>PHI2045S</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>368</v>
+      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="26.39999961853027" customHeight="1">
+      <c r="A21" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>REL1002F</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>434</v>
+      </c>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="26.39999961853027" customHeight="1">
+      <c r="A22" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>REL2040F</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="26.39999961853027" customHeight="1">
+      <c r="A23" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>REL2040F</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>2 of 2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>One tutorial is listed without a day or time. The lecture days and period do not specify the tutorial schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26.39999961853027" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>REL2047F</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="26.39999961853027" customHeight="1">
+      <c r="A25" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>SLL1136S</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>The 6th period is printed without weekdays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="39.59999847412109" customHeight="1">
+      <c r="A26" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>SOC1001F</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>First of the two stated alternatives: 4th period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.59999847412109" customHeight="1">
+      <c r="A27" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>SOC1005S</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>1 of 2</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday, Wednesday, Thursday</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>First of the two stated alternatives: 4th period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="39.59999847412109" customHeight="1">
+      <c r="A28" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>SLL1017S</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>The heading is SLL1017FS on p. 244. Its lecture time continues on p. 245 and gives the 7th period without weekdays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39.59999847412109" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>SLL1022F</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Friday</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="39.59999847412109" customHeight="1">
+      <c r="A30" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>SLL1018S</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>249</v>
+      </c>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="39.59999847412109" customHeight="1">
+      <c r="A31" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>SLL1101F</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>249</v>
+      </c>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="39.59999847412109" customHeight="1">
+      <c r="A32" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>SLL1058F</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="39.59999847412109" customHeight="1">
+      <c r="A33" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>SLL1059S</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="39.59999847412109" customHeight="1">
+      <c r="A34" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>SLL1051S</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>264</v>
+      </c>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="26.39999961853027" customHeight="1">
+      <c r="A35" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>SLL1060F</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>3 of 3</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>conversation</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>273</v>
+      </c>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>One conversation class per week is listed without a day or time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="39.59999847412109" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>161</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>SLL1065S</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="39.59999847412109" customHeight="1">
+      <c r="A37" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>SLL1075F</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>1 of 4</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>First stated lecture alternative: 1st period, rather than the meridian alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26.39999961853027" customHeight="1">
+      <c r="A38" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>SLL1075F</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>4 of 4</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>conversation</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>One conversation class is listed without a day or time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="39.59999847412109" customHeight="1">
+      <c r="A39" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>SLL1076S</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>1 of 4</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>First stated lecture alternative: 1st period, rather than the meridian alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26.39999961853027" customHeight="1">
+      <c r="A40" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>SLL1076S</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>3 of 4</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>One tutorial is listed without a day or time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="39.59999847412109" customHeight="1">
+      <c r="A41" s="5" t="n">
         <v>174</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>SLL1073F</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>1 of 1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>lecture</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>University of Cape Town, Faculty of Humanities (Undergraduate), 2026</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1421,7 +2334,7 @@
       <formula1>"yes"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1487,6 +2400,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>